--- a/docs/MANUAL_TEST_CHECKLIST.xlsx
+++ b/docs/MANUAL_TEST_CHECKLIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_software\work_project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA09F19-9F7E-410F-8C7C-7149338FB4F7}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465113EB-F3D8-4218-96F2-BCD40F2C0425}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="315">
   <si>
     <t>Тип</t>
   </si>
@@ -727,9 +727,6 @@
     <t>Элементы не наслаиваются, подписи и легенда графиков читаемы</t>
   </si>
   <si>
-    <t>id 05</t>
-  </si>
-  <si>
     <t>UI-09</t>
   </si>
   <si>
@@ -796,9 +793,6 @@
     <t>Кнопка оплаты, суммы и подписи не перекрывают друг друга</t>
   </si>
   <si>
-    <t>id 12</t>
-  </si>
-  <si>
     <t>UI-16</t>
   </si>
   <si>
@@ -940,58 +934,40 @@
     <t>Низких багов</t>
   </si>
   <si>
-    <t>Знак вопроса для всплывающей подсказки некрасивый. Сделай его в виде просто значка вопроса с небольшой прозрачностью (без всяких рамок обводки)</t>
-  </si>
-  <si>
-    <t>В карточках объектов размести логотип-иконку по центру по высоте. Также в случае если домофон не указан - не пиши фразу "Доофон:…" - просто центрируй адрес и инфо о заказчике по высоте (дату оставляй как есть сейчас</t>
-  </si>
-  <si>
-    <t>Из-за выезжающей клавиатуры на мобайле результатов поиска визуально отображается совсем немного. Предлагаю решение: доделать функционал "подъема" поисковой строки при фокусе. Сейчас она уже поднимается при нажатии на нее, однако при начале ввода текста она опять возвращается на прежнее место, а нужно чтобы она оставалась верху экрана, что обеспечит отображение большего кол-ва найденных результатов.</t>
-  </si>
-  <si>
-    <t>В случае вертикальной ориентации в графиках динамики работ отражаются сразу 2 логотипа-картинки для переворачивания экрана. Это ошибка. Также еще 1 проблема: если пользователь переворачивает телефон горизонтально - графики отображаются как и должны, однако в этом случае шапка занимает слишком много места и графики плохо читабельны из-за этого.</t>
-  </si>
-  <si>
-    <t>Нужно заменять "Мес" на "Месяц"</t>
-  </si>
-  <si>
-    <t>кнопки действий (редактирование и удаление) на карточке объекта находятся на неверной высоте. Нужно чтобы если строка с адресом объекта одна - одни располагались на такой же высоте в блоке, а если строк больше - то они долны быть на высоте первой строки.</t>
-  </si>
-  <si>
-    <t>id 06</t>
-  </si>
-  <si>
-    <t>Кнопка сохранения файла не работает (по-моему она выполняет сейчас такую же функцию, как и кнопка "Поделиться"). Я хочу чтобы была возможность сохранения файла именно с путем его сохранения в файловой системе телефона. Также всплывающая подсказка внизу экрана сейчас не локализована на русский язык и может не соответствовать действительности (например она может уведомлять об успешнй загрузке, однако загрузка файла была отменена)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Небольшая карточка с указанием источника объекта в случае если адрес короткий - находится по-центру строк с адресом объекта. В случае если строк больше одной - пусть эта карточка располагается так же, как и в случае с 1 строкой </t>
-  </si>
-  <si>
-    <t>В силовом щите при открытии диалогового окна добавления позиции и дальнейшего открытия выпадающих списков Номинал и Тиа - элементы этих списков располагаются на прозрачном фоне и из-за этого видно задний план. Нужно убрать прозрачность. Также кнопки действий шаблоны, заметки, редактирование итд) давай во всех щитах размести по центру по ширине.</t>
-  </si>
-  <si>
-    <t>Все диалоги доступны, однако если в диалоге предусмотрена прокрутка (она работает) - пользователь не видит, что диалог можно прокрутить еще вниз если у него отображается верхняя часть. Сейчас по таким диалогам добавлены надписи типа "Scroll for full content" - нужно удалить везде такие надписи. В случае, если пользователь сталкивается с такими сценариями (видит только вернюю часть всего диалогового окна, а продолжение скрыто из-за размера экрана - давай сделаем всегда видимой полосу прокрутки справа.</t>
-  </si>
-  <si>
-    <t>Нужно заменить слово Total на Всего</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заменим слова Свет и Темн в переключателе темы на соответствующие иконки. Также в разделе с переключением начального экрана давай отделим зону сврху (логотип, заголовок, тогл) и нижнюю зону (сделаем там просто описание относительно мелким шрифтом. </t>
-  </si>
-  <si>
     <t>id 7</t>
   </si>
   <si>
     <t>id 8</t>
   </si>
   <si>
-    <t>id 9</t>
-  </si>
-  <si>
-    <t>id 10</t>
-  </si>
-  <si>
-    <t>id  11</t>
+    <t>Знак вопроса для всплывающей подсказки сделай просто в виде вопросительного знака (без обводки круга)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В карточках объектов следующее содержимой всегда нужно центроровать по высоте (адерс, информация о закзачике, домофон). Имею в виду что вне зависимости от того, сколько из этих 3 пунктов существуют в объекте - они всегда должны центрироваться: если 1 - то он по центру по высоте, если 2 - то они тоже отцентрированы, если 3 - тоже </t>
+  </si>
+  <si>
+    <t>строка поиска при наведении курсора и нажатии на нее оказывается слишком высоко (нужно немного отсутпать от верха чтобы строка поиска не залазила на системные значки андроида). Строка поиска при введении символа (и нахождении результатов) должна оставаться на той же высоте, а не опускаться под 3 карточки "предпрсчеты, теккущие, оплачено)</t>
+  </si>
+  <si>
+    <t>Кнопка сохранения файла не работает - при выборе папке и нажатии кнопки "выбрать" появляется ошибка</t>
+  </si>
+  <si>
+    <t>кнопки действий (редактирование и удаление) на карточке объекта находятся на неверной высоте. Нужно чтобы если строка с адресом объекта одна - они визуально располагались на такой же высоте (а если строк больше - то они долны быть такой же высоте, как и первая строка). пример - крестик удаления в меню "Этапы"</t>
+  </si>
+  <si>
+    <t>В силовом щите при открытии диалогового окна добавления позиции и дальнейшего открытия выпадающих списков Номинал и Тип устройства, Полюса - элементы этих списков плохо отличимы друг от друга. нужно добавить разделитель (пример - в диалоговом окне кнопки "Добавить щит")Также кнопки действий шаблоны, заметки, редактирование итд) во всех щитах нужно разместить в центре блока по ширине (сейчас они смещены к левому краю)</t>
+  </si>
+  <si>
+    <t>Если в диалоговом окне предусмотрена прокрутка содержимого - пользователь не видит, что диалог можно прокрутить еще вниз и у него отображается верхняя часть. Сейчас по таким диалогам добавлены надписи типа "Scroll for full content" - нужно удалить везде такие надписи. В случае, если пользователь сталкивается с такими сценариями (видит только вернюю часть всего диалогового окна, а продолжение скрыто из-за размера экрана - давай сделаем всегда видимой полосу прокрутки справа. полоса должна подходить по стилю к диалоговому окну</t>
+  </si>
+  <si>
+    <t>Замени иконку в переключателе темы с системы - на слово "Авто", визуально отдели на 2 блока тему приложения и начальный экран (и описание этого пункта)</t>
+  </si>
+  <si>
+    <t>id 5</t>
+  </si>
+  <si>
+    <t>id 6</t>
   </si>
 </sst>
 </file>
@@ -2693,7 +2669,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>200</v>
       </c>
@@ -2777,17 +2753,11 @@
         <v>229</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>308</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="4"/>
     </row>
     <row r="56" spans="1:10" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
@@ -2823,29 +2793,23 @@
         <v>69</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E57" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="F57" s="4" t="s">
-        <v>237</v>
-      </c>
       <c r="G57" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I57" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>309</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="4"/>
     </row>
     <row r="58" spans="1:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
@@ -2855,16 +2819,16 @@
         <v>73</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E58" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>215</v>
@@ -2873,10 +2837,10 @@
         <v>216</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>311</v>
+        <v>230</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2887,16 +2851,16 @@
         <v>78</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>75</v>
       </c>
       <c r="E59" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>243</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>40</v>
@@ -2913,16 +2877,16 @@
         <v>82</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E60" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>245</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>246</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>40</v>
@@ -2939,16 +2903,16 @@
         <v>87</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E61" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>248</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>249</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>40</v>
@@ -2965,28 +2929,28 @@
         <v>91</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>127</v>
       </c>
       <c r="E62" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>252</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>215</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2997,29 +2961,23 @@
         <v>96</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>161</v>
       </c>
       <c r="E63" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>256</v>
-      </c>
       <c r="G63" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>313</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="4"/>
     </row>
     <row r="64" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
@@ -3029,16 +2987,16 @@
         <v>100</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>161</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>40</v>
@@ -3047,7 +3005,7 @@
       <c r="I64" s="5"/>
       <c r="J64" s="4"/>
     </row>
-    <row r="65" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>200</v>
       </c>
@@ -3055,16 +3013,16 @@
         <v>104</v>
       </c>
       <c r="C65" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E65" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="F65" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>264</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>215</v>
@@ -3073,10 +3031,10 @@
         <v>225</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3087,16 +3045,16 @@
         <v>108</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>267</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>40</v>
@@ -3113,28 +3071,28 @@
         <v>112</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E67" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="F67" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>271</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>215</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3145,29 +3103,23 @@
         <v>117</v>
       </c>
       <c r="C68" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="F68" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>274</v>
-      </c>
       <c r="G68" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="J68" s="4" t="s">
-        <v>316</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="4"/>
     </row>
     <row r="69" spans="1:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
@@ -3177,16 +3129,16 @@
         <v>121</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E69" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="F69" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>278</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>215</v>
@@ -3195,10 +3147,10 @@
         <v>225</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -3209,16 +3161,16 @@
         <v>125</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E70" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="F70" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>40</v>
@@ -3235,16 +3187,16 @@
         <v>130</v>
       </c>
       <c r="C71" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E71" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="F71" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>286</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>40</v>
@@ -3255,7 +3207,7 @@
     </row>
     <row r="72" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B72" s="3"/>
       <c r="C72" s="2"/>
@@ -3271,17 +3223,17 @@
     </row>
     <row r="73" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2" t="s">
@@ -3293,17 +3245,17 @@
     </row>
     <row r="74" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2" t="s">
@@ -3315,14 +3267,14 @@
     </row>
     <row r="75" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>100</v>
@@ -3337,14 +3289,14 @@
     </row>
     <row r="76" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B76" s="3"/>
       <c r="C76" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>35</v>
@@ -3359,14 +3311,14 @@
     </row>
     <row r="77" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>41</v>
@@ -3381,14 +3333,14 @@
     </row>
     <row r="78" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>45</v>
@@ -3403,14 +3355,14 @@
     </row>
     <row r="79" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B79" s="3"/>
       <c r="C79" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>49</v>
@@ -3425,14 +3377,14 @@
     </row>
     <row r="80" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>23</v>

--- a/docs/MANUAL_TEST_CHECKLIST.xlsx
+++ b/docs/MANUAL_TEST_CHECKLIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_software\work_project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465113EB-F3D8-4218-96F2-BCD40F2C0425}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66FC130-295E-4168-9C8B-2C15103417E8}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="309">
   <si>
     <t>Тип</t>
   </si>
@@ -715,9 +715,6 @@
     <t>Блоки адаптивно перестраиваются, без наложений</t>
   </si>
   <si>
-    <t>id 04</t>
-  </si>
-  <si>
     <t>UI-08</t>
   </si>
   <si>
@@ -934,40 +931,25 @@
     <t>Низких багов</t>
   </si>
   <si>
-    <t>id 7</t>
-  </si>
-  <si>
-    <t>id 8</t>
-  </si>
-  <si>
-    <t>Знак вопроса для всплывающей подсказки сделай просто в виде вопросительного знака (без обводки круга)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">В карточках объектов следующее содержимой всегда нужно центроровать по высоте (адерс, информация о закзачике, домофон). Имею в виду что вне зависимости от того, сколько из этих 3 пунктов существуют в объекте - они всегда должны центрироваться: если 1 - то он по центру по высоте, если 2 - то они тоже отцентрированы, если 3 - тоже </t>
-  </si>
-  <si>
-    <t>строка поиска при наведении курсора и нажатии на нее оказывается слишком высоко (нужно немного отсутпать от верха чтобы строка поиска не залазила на системные значки андроида). Строка поиска при введении символа (и нахождении результатов) должна оставаться на той же высоте, а не опускаться под 3 карточки "предпрсчеты, теккущие, оплачено)</t>
-  </si>
-  <si>
-    <t>Кнопка сохранения файла не работает - при выборе папке и нажатии кнопки "выбрать" появляется ошибка</t>
-  </si>
-  <si>
-    <t>кнопки действий (редактирование и удаление) на карточке объекта находятся на неверной высоте. Нужно чтобы если строка с адресом объекта одна - они визуально располагались на такой же высоте (а если строк больше - то они долны быть такой же высоте, как и первая строка). пример - крестик удаления в меню "Этапы"</t>
-  </si>
-  <si>
-    <t>В силовом щите при открытии диалогового окна добавления позиции и дальнейшего открытия выпадающих списков Номинал и Тип устройства, Полюса - элементы этих списков плохо отличимы друг от друга. нужно добавить разделитель (пример - в диалоговом окне кнопки "Добавить щит")Также кнопки действий шаблоны, заметки, редактирование итд) во всех щитах нужно разместить в центре блока по ширине (сейчас они смещены к левому краю)</t>
-  </si>
-  <si>
-    <t>Если в диалоговом окне предусмотрена прокрутка содержимого - пользователь не видит, что диалог можно прокрутить еще вниз и у него отображается верхняя часть. Сейчас по таким диалогам добавлены надписи типа "Scroll for full content" - нужно удалить везде такие надписи. В случае, если пользователь сталкивается с такими сценариями (видит только вернюю часть всего диалогового окна, а продолжение скрыто из-за размера экрана - давай сделаем всегда видимой полосу прокрутки справа. полоса должна подходить по стилю к диалоговому окну</t>
-  </si>
-  <si>
-    <t>Замени иконку в переключателе темы с системы - на слово "Авто", визуально отдели на 2 блока тему приложения и начальный экран (и описание этого пункта)</t>
-  </si>
-  <si>
     <t>id 5</t>
   </si>
   <si>
-    <t>id 6</t>
+    <t>Знак вопроса для всплывающей подсказки нужно сделать боее прозрачным. Так же нужно изменить аналогичный значок в разделе статистики (на графиках) на такой же.</t>
+  </si>
+  <si>
+    <t>при вводе символа в строку поиска - строка меняет свое местоположение на экране (на экране снова видны карточки Предпросчеты, Текущие, Оплачено выше строки поиска). Строка поиска должна оставаться вверху экрана (это сделано для отображения большего кол-ва результатов поисковой выдачи)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">кнопки редактирвания и удаления на карточке объекта находятся на неверной высоте: нужно чтобы они находились на одной (идеально одинаковой) высоте с первой строкой названия объекта. пример - крестик удаления в меню "Этапы". </t>
+  </si>
+  <si>
+    <t>Кнопка сохранения файла не работает - при нажатии выдает ошибку</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В диалоговых окнах где предусмотрена полоса прокрутки - нужно сделать ее дизайн более "плавным" </t>
+  </si>
+  <si>
+    <t>id 4</t>
   </si>
 </sst>
 </file>
@@ -2666,7 +2648,7 @@
         <v>217</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2689,17 +2671,11 @@
         <v>220</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>306</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="4"/>
     </row>
     <row r="54" spans="1:10" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
@@ -2727,10 +2703,10 @@
         <v>225</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="81" customHeight="1" x14ac:dyDescent="0.25">
@@ -2767,16 +2743,16 @@
         <v>65</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E56" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F56" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>233</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>40</v>
@@ -2793,16 +2769,16 @@
         <v>69</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E57" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>40</v>
@@ -2811,7 +2787,7 @@
       <c r="I57" s="5"/>
       <c r="J57" s="4"/>
     </row>
-    <row r="58" spans="1:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>200</v>
       </c>
@@ -2819,16 +2795,16 @@
         <v>73</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E58" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>239</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>215</v>
@@ -2837,10 +2813,10 @@
         <v>216</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2851,16 +2827,16 @@
         <v>78</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>75</v>
       </c>
       <c r="E59" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>242</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>40</v>
@@ -2877,16 +2853,16 @@
         <v>82</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E60" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>245</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>40</v>
@@ -2903,16 +2879,16 @@
         <v>87</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E61" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>40</v>
@@ -2929,28 +2905,28 @@
         <v>91</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>127</v>
       </c>
       <c r="E62" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>215</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2961,16 +2937,16 @@
         <v>96</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>161</v>
       </c>
       <c r="E63" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>255</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>40</v>
@@ -2987,16 +2963,16 @@
         <v>100</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>161</v>
       </c>
       <c r="E64" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>40</v>
@@ -3013,29 +2989,23 @@
         <v>104</v>
       </c>
       <c r="C65" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="E65" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="F65" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>262</v>
-      </c>
       <c r="G65" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>310</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="4"/>
     </row>
     <row r="66" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
@@ -3045,16 +3015,16 @@
         <v>108</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E66" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E66" s="4" t="s">
+      <c r="F66" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>265</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>40</v>
@@ -3071,28 +3041,28 @@
         <v>112</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="E67" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="F67" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>215</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3103,16 +3073,16 @@
         <v>117</v>
       </c>
       <c r="C68" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E68" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E68" s="4" t="s">
+      <c r="F68" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>40</v>
@@ -3129,29 +3099,23 @@
         <v>121</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="E69" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="F69" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="F69" s="4" t="s">
-        <v>276</v>
-      </c>
       <c r="G69" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="I69" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>312</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="4"/>
     </row>
     <row r="70" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
@@ -3161,16 +3125,16 @@
         <v>125</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="E70" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="F70" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>40</v>
@@ -3187,16 +3151,16 @@
         <v>130</v>
       </c>
       <c r="C71" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="E71" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="F71" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>40</v>
@@ -3207,7 +3171,7 @@
     </row>
     <row r="72" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B72" s="3"/>
       <c r="C72" s="2"/>
@@ -3223,17 +3187,17 @@
     </row>
     <row r="73" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2" t="s">
@@ -3245,17 +3209,17 @@
     </row>
     <row r="74" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D74" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2" t="s">
@@ -3267,14 +3231,14 @@
     </row>
     <row r="75" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>100</v>
@@ -3289,14 +3253,14 @@
     </row>
     <row r="76" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B76" s="3"/>
       <c r="C76" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>35</v>
@@ -3311,14 +3275,14 @@
     </row>
     <row r="77" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>41</v>
@@ -3333,14 +3297,14 @@
     </row>
     <row r="78" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>45</v>
@@ -3355,14 +3319,14 @@
     </row>
     <row r="79" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B79" s="3"/>
       <c r="C79" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>49</v>
@@ -3377,14 +3341,14 @@
     </row>
     <row r="80" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>23</v>
